--- a/TX2/TH4/Dynamic Programming/example_01knapsack.xlsx
+++ b/TX2/TH4/Dynamic Programming/example_01knapsack.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UDTT\TX2\TH4\Dynamic Programming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{048161A2-B87F-491C-B903-8255DF2FB0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E942B626-285D-4788-B1E7-8DA7EF563888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12624" yWindow="0" windowWidth="10512" windowHeight="12336" xr2:uid="{789CCAFF-FF59-4567-9A01-0402FB681F46}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{789CCAFF-FF59-4567-9A01-0402FB681F46}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -974,7 +974,7 @@
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
